--- a/Budgeting System_User Management.xlsx
+++ b/Budgeting System_User Management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281FC460-7CBA-46FF-B3CC-DD1CAF0D490F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6ABAB2-22B0-4DEC-9341-94CDF73F189F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{BBB40E87-344D-44B7-9B1E-15C800564467}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{BBB40E87-344D-44B7-9B1E-15C800564467}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="13" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">CD!$A$1:$D$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MC!$A$1:$C$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">NCD!$A$1:$C$276</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">NPC!$A$1:$Y$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">NPC!$A$1:$Y$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">SF!$A$1:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'User List'!$A$1:$G$350</definedName>
   </definedNames>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3580" uniqueCount="1059">
   <si>
     <t>Name</t>
   </si>
@@ -3226,13 +3226,19 @@
   </si>
   <si>
     <t>Manpower Preparer</t>
+  </si>
+  <si>
+    <t>SBU Finance Head</t>
+  </si>
+  <si>
+    <t>SBU Finance Reviewer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3278,6 +3284,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3296,10 +3310,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3338,11 +3353,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10441,7 +10478,7 @@
       <c r="A308" t="s">
         <v>476</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="14" t="s">
         <v>128</v>
       </c>
       <c r="C308" t="s">
@@ -11329,8 +11366,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G350" xr:uid="{CECB4391-08FC-4FB8-B4E1-C3083BBE8EA8}"/>
+  <hyperlinks>
+    <hyperlink ref="B308" r:id="rId1" xr:uid="{07F8086D-7A7D-4E4D-9ABF-55EA76B0C645}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -12927,32 +12967,32 @@
   </sheetData>
   <autoFilter ref="A1:D57" xr:uid="{F73EFF81-431E-4648-9DA9-FC095CAD4E4B}"/>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B57">
-    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B57">
-    <cfRule type="duplicateValues" dxfId="31" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C44">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C44">
-    <cfRule type="duplicateValues" dxfId="28" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16104,18 +16144,18 @@
   </sheetData>
   <autoFilter ref="A1:C6" xr:uid="{DD9C9D26-F4C8-4414-AA1F-561005E3B0BD}"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A7">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16177,20 +16217,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16198,15 +16238,16 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B762F45E-143D-4C65-875A-C8956B26B1CD}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -16216,8 +16257,11 @@
       <c r="C1" s="9" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="9" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>482</v>
       </c>
@@ -16227,8 +16271,11 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>480</v>
       </c>
@@ -16238,8 +16285,11 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>481</v>
       </c>
@@ -16249,8 +16299,11 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>678</v>
       </c>
@@ -16260,8 +16313,11 @@
       <c r="C5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>613</v>
       </c>
@@ -16272,7 +16328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>681</v>
       </c>
@@ -16282,8 +16338,11 @@
       <c r="C7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>806</v>
       </c>
@@ -16294,7 +16353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>620</v>
       </c>
@@ -16304,8 +16363,11 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>625</v>
       </c>
@@ -16315,8 +16377,11 @@
       <c r="C10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>687</v>
       </c>
@@ -16326,8 +16391,11 @@
       <c r="C11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>688</v>
       </c>
@@ -16337,8 +16405,11 @@
       <c r="C12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>628</v>
       </c>
@@ -16348,8 +16419,11 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>807</v>
       </c>
@@ -16359,8 +16433,11 @@
       <c r="C14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>807</v>
       </c>
@@ -16369,27 +16446,30 @@
       </c>
       <c r="C15" t="s">
         <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C15" xr:uid="{B762F45E-143D-4C65-875A-C8956B26B1CD}"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A15">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A15">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B4">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16397,7 +16477,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8871DFD7-96A4-45C4-AEEA-7CE912124976}">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -16649,43 +16729,43 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>677</v>
-      </c>
-      <c r="B23" t="s">
-        <v>151</v>
+        <v>974</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>678</v>
-      </c>
-      <c r="B24" t="s">
-        <v>152</v>
+        <v>974</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>679</v>
-      </c>
-      <c r="B25" t="s">
-        <v>153</v>
+        <v>974</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>4</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -16693,10 +16773,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -16704,10 +16784,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -16715,10 +16795,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -16726,10 +16806,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -16737,10 +16817,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -16748,10 +16828,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -16759,10 +16839,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -16770,10 +16850,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -16781,10 +16861,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -16792,10 +16872,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -16803,10 +16883,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -16814,10 +16894,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B38" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -16825,10 +16905,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B39" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -16836,10 +16916,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -16847,10 +16927,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -16858,10 +16938,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -16869,10 +16949,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>706</v>
+        <v>684</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
@@ -16880,10 +16960,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
@@ -16891,10 +16971,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B45" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
@@ -16902,10 +16982,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
@@ -16913,10 +16993,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
@@ -16924,10 +17004,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
@@ -16935,10 +17015,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="B49" t="s">
-        <v>306</v>
+        <v>222</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
@@ -16946,10 +17026,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>686</v>
+        <v>710</v>
       </c>
       <c r="B50" t="s">
-        <v>321</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -16957,10 +17037,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B51" t="s">
-        <v>343</v>
+        <v>231</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
@@ -16968,10 +17048,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B52" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="C52" t="s">
         <v>4</v>
@@ -16979,10 +17059,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
@@ -16990,10 +17070,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="B54" t="s">
-        <v>403</v>
+        <v>343</v>
       </c>
       <c r="C54" t="s">
         <v>4</v>
@@ -17001,10 +17081,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B55" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="C55" t="s">
         <v>4</v>
@@ -17012,10 +17092,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="B56" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="C56" t="s">
         <v>4</v>
@@ -17023,10 +17103,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>713</v>
       </c>
       <c r="B57" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C57" t="s">
         <v>4</v>
@@ -17034,10 +17114,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B58" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -17045,10 +17125,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B59" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="C59" t="s">
         <v>4</v>
@@ -17056,10 +17136,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>718</v>
+        <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C60" t="s">
         <v>4</v>
@@ -17067,43 +17147,43 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>618</v>
+        <v>716</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>427</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>664</v>
+        <v>717</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>619</v>
+        <v>718</v>
       </c>
       <c r="B63" t="s">
-        <v>176</v>
+        <v>431</v>
       </c>
       <c r="C63" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>543</v>
+        <v>618</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -17111,10 +17191,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>664</v>
       </c>
       <c r="B65" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -17122,10 +17202,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>544</v>
+        <v>619</v>
       </c>
       <c r="B66" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -17133,10 +17213,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -17144,10 +17224,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>663</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -17155,10 +17235,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B69" t="s">
-        <v>327</v>
+        <v>199</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -17166,10 +17246,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>620</v>
+        <v>545</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>210</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -17177,10 +17257,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>621</v>
+        <v>663</v>
       </c>
       <c r="B71" t="s">
-        <v>411</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -17188,43 +17268,43 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>607</v>
+        <v>546</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>328</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>411</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>607</v>
       </c>
       <c r="B75" t="s">
-        <v>317</v>
+        <v>160</v>
       </c>
       <c r="C75" t="s">
         <v>6</v>
@@ -17232,10 +17312,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B76" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
         <v>6</v>
@@ -17243,10 +17323,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B77" t="s">
-        <v>416</v>
+        <v>258</v>
       </c>
       <c r="C77" t="s">
         <v>6</v>
@@ -17254,10 +17334,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>614</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="C78" t="s">
         <v>6</v>
@@ -17265,10 +17345,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s">
-        <v>433</v>
+        <v>338</v>
       </c>
       <c r="C79" t="s">
         <v>6</v>
@@ -17276,10 +17356,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B80" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C80" t="s">
         <v>6</v>
@@ -17287,10 +17367,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>807</v>
+        <v>614</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>424</v>
       </c>
       <c r="C81" t="s">
         <v>6</v>
@@ -17298,54 +17378,54 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>807</v>
+        <v>612</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>433</v>
       </c>
       <c r="C82" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>738</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>436</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>739</v>
+        <v>807</v>
       </c>
       <c r="B84" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="B86" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C86" t="s">
         <v>7</v>
@@ -17353,10 +17433,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="C87" t="s">
         <v>7</v>
@@ -17364,10 +17444,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="C88" t="s">
         <v>7</v>
@@ -17375,10 +17455,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="B89" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="C89" t="s">
         <v>7</v>
@@ -17386,10 +17466,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B90" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -17397,10 +17477,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="B91" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
@@ -17408,10 +17488,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>744</v>
+        <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>325</v>
+        <v>247</v>
       </c>
       <c r="C92" t="s">
         <v>7</v>
@@ -17419,10 +17499,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="B93" t="s">
-        <v>329</v>
+        <v>250</v>
       </c>
       <c r="C93" t="s">
         <v>7</v>
@@ -17430,10 +17510,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
       <c r="B94" t="s">
-        <v>340</v>
+        <v>255</v>
       </c>
       <c r="C94" t="s">
         <v>7</v>
@@ -17441,10 +17521,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="B95" t="s">
-        <v>382</v>
+        <v>256</v>
       </c>
       <c r="C95" t="s">
         <v>7</v>
@@ -17452,10 +17532,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="B96" t="s">
-        <v>405</v>
+        <v>259</v>
       </c>
       <c r="C96" t="s">
         <v>7</v>
@@ -17463,10 +17543,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>759</v>
       </c>
       <c r="B97" t="s">
-        <v>422</v>
+        <v>260</v>
       </c>
       <c r="C97" t="s">
         <v>7</v>
@@ -17474,17 +17554,231 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B98" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="C98" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>765</v>
+      </c>
+      <c r="B99" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>766</v>
+      </c>
+      <c r="B100" t="s">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>751</v>
+      </c>
+      <c r="B101" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>767</v>
+      </c>
+      <c r="B102" t="s">
+        <v>271</v>
+      </c>
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>768</v>
+      </c>
+      <c r="B103" t="s">
+        <v>277</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>752</v>
+      </c>
+      <c r="B104" t="s">
+        <v>278</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>753</v>
+      </c>
+      <c r="B105" t="s">
+        <v>279</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>754</v>
+      </c>
+      <c r="B106" t="s">
+        <v>290</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>760</v>
+      </c>
+      <c r="B107" t="s">
+        <v>348</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>728</v>
+      </c>
+      <c r="B108" t="s">
+        <v>238</v>
+      </c>
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>622</v>
+      </c>
+      <c r="B109" t="s">
+        <v>241</v>
+      </c>
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>623</v>
+      </c>
+      <c r="B110" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>624</v>
+      </c>
+      <c r="B111" t="s">
+        <v>272</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>806</v>
+      </c>
+      <c r="B112" t="s">
+        <v>274</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>625</v>
+      </c>
+      <c r="B113" t="s">
+        <v>339</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>626</v>
+      </c>
+      <c r="B114" t="s">
+        <v>366</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>627</v>
+      </c>
+      <c r="B115" t="s">
+        <v>394</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>628</v>
+      </c>
+      <c r="B116" t="s">
+        <v>397</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>629</v>
+      </c>
+      <c r="B117" t="s">
+        <v>406</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y98" xr:uid="{8871DFD7-96A4-45C4-AEEA-7CE912124976}"/>
+  <autoFilter ref="A1:Y117" xr:uid="{8871DFD7-96A4-45C4-AEEA-7CE912124976}"/>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>